--- a/www/download/COUNTRY.MLT.rpPE.xlsx
+++ b/www/download/COUNTRY.MLT.rpPE.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.821684755536959</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.839100636076563</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.898078280441284</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.904384898541739</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.929851826238597</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.01871863654664</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.04756224641374</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.00792264839678</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.877192137997102</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.802021683764487</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.804162377075274</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.793408381912368</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.724495030641948</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.679660773115357</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.716576242819136</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.640529919255068</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.533617976314131</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.536280994976895</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.47793506564853</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.509439187209727</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.586837819722745</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.254891174697205</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.374616184492265</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.488311157306391</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.207807130614602</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.194867186940659</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0.19265219914381</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.175972084374396</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.0977202708596596</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.0806876510689012</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.254306595045285</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.192391747270681</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.18366697740047</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.114061594726557</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.13821215222682</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.184338312277557</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>-0.0523959948178461</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.0448844799601507</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.191886006493292</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>-0.113627455997533</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>-0.075569557300181</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>-0.0691407435799243</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.0422154815962821</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>-0.12317256693918</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>-0.126982369627044</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>272.138</t>
+          <t>-0.48868507058924</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>273.341</t>
+          <t>-0.497468082412896</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>274.43</t>
+          <t>-0.498893366217405</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>278.239</t>
+          <t>-0.551382701570597</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>282.002</t>
+          <t>-0.542980620366423</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>285.185</t>
+          <t>-0.534684589450449</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>244.532</t>
+          <t>-0.625243970368378</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>288.899</t>
+          <t>-0.583165450757734</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>277.161</t>
+          <t>-0.66582798583928</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>-0.626867130127967</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>286.041</t>
+          <t>-0.597919703738308</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>287.987</t>
+          <t>-0.590513970855364</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>300.123</t>
+          <t>-0.554019920433488</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>306.883</t>
+          <t>-0.608767791662913</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>307.78</t>
+          <t>-0.604496670308628</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>239.98</t>
+          <t>787624029.272906</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>241.04</t>
+          <t>775415400.071434</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>242.001</t>
+          <t>657843926.503165</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>245.359</t>
+          <t>735589072.330446</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>248.678</t>
+          <t>868890713.23994</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>251.485</t>
+          <t>1044003748.90968</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>216.96</t>
+          <t>847892378.226845</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>256.499</t>
+          <t>864158047.266202</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>245.286</t>
+          <t>847471308.003418</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>250.577</t>
+          <t>864545320.170048</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>252.301</t>
+          <t>808226337.573305</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>253.898</t>
+          <t>887050598.713625</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>264.56</t>
+          <t>836181568.865398</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>271.437</t>
+          <t>840103487.4604</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>264.649</t>
+          <t>752717910.282848</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>556100296.141532</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>576149951.751794</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>575747934.400681</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>642973173.821213</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>648345474.426813</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>648997087.36027</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>702041333.566067</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>748019413.255718</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>773817638.838697</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>847806579.750752</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>808548851.090347</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>801214100.69862</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>771759245.883185</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>865291927.933365</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>862057058.816201</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>4533158.46039863</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>4379308.02507642</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>3900965.9223749</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>4012397.07174443</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>4538670.61582515</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>5034282.0684565</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>4477952.91579446</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>4285935.24463161</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>3545666.13334383</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>3334622.97706303</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>2888729.37490377</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>3162680.42900055</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>2504244.65110953</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>2230407.83465025</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>2363622.60430178</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>1081.51294717871</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>1076.04346394231</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>1020.59954525404</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>981.288096912751</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>1029.63491017034</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>1050.72048986818</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>885.010743328213</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>1050.58164600886</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>1121.30660632351</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>1318.07254465421</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>1366.66051193781</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>1437.37306171148</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>1594.61006750721</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>1735.22894987053</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>1652.28386555998</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>2598.70652356826</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>2588.09265919899</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>2148.1784694281</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>2278.91479674516</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>2725.23416328149</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>3185.70454440644</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>23.74</t>
+          <t>2495.75869719706</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>2611.55846952112</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>2969.28229099837</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>3146.67344772498</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>3187.33595512157</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>3719.76861198699</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>4144.71321433078</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>4731.45290242625</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>3905.09683640545</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>-0.117601198538701</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>-0.144954385510027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>-0.162645922045133</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>-0.238816290468603</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>-0.209665892554193</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>-0.17252015605038</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>-0.330731199166461</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>-0.258773624341776</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>26.33</t>
+          <t>-0.318100025984723</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>-0.304637565028544</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>-0.273054625996913</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>-0.259399755119709</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>-0.237468447396964</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>26.27</t>
+          <t>-0.314259040460635</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>-0.293290281113408</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>935.033766716748</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>962.436088886035</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>51.91</t>
+          <t>878.112097574302</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>53.05</t>
+          <t>988.361789538299</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>1028.45972006696</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>1079.4579623307</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>47.53</t>
+          <t>862.927322251072</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>47.26</t>
+          <t>857.643554506389</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>46.13</t>
+          <t>1092.12927592513</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>1192.83169298121</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>1235.83258064407</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>1428.20462482944</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>42.79</t>
+          <t>1649.43198151582</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>42.07</t>
+          <t>1868.92749049352</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>39.09</t>
+          <t>1817.72581885165</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.821684755536959</t>
+          <t>4540.93849068261</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.839100636076563</t>
+          <t>4683.95486188163</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.898078280441284</t>
+          <t>4662.1039309677</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.904384898541739</t>
+          <t>5135.19683558146</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.929851826238597</t>
+          <t>5108.99711869927</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.01871863654664</t>
+          <t>5057.05167385274</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.04756224641374</t>
+          <t>5327.65823050692</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.00792264839678</t>
+          <t>5567.51092975044</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.877192137997102</t>
+          <t>5806.66008413902</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.802021683764487</t>
+          <t>6456.78603624533</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.804162377075274</t>
+          <t>6073.9319555743</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.793408381912368</t>
+          <t>5893.88991342041</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.724495030641948</t>
+          <t>5502.43159054018</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679660773115357</t>
+          <t>6029.75083571161</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716576242819136</t>
+          <t>5966.10112253914</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>53764545.5703927</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>88199913.0851514</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>58485334.1536882</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>116868623.340699</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>196267392.059141</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>251313223.364969</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>292054619.839381</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>354783223.997211</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>331790047.480739</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>171687258.291193</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>222045049.808534</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>267700748.209984</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>300569819.851359</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>348523930.572587</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>295252497.073781</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-40750659.7064369</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-15445123.5265529</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-47416106.260441</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-10003990.0722663</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>44258185.2647322</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>76444858.2090662</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>165615478.462675</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>183891403.747334</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>183925110.283326</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-669597.81094526</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>53301533.5037203</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>91396360.1867754</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>90483128.2321351</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>103483511.117064</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>32480551.5401076</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>94515205.2768297</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>103645036.611704</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>105901440.414129</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>126872613.412965</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>152009206.794409</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>174868365.155903</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>126439141.376706</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>170891820.249877</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>147864937.197414</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>172356856.102138</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>168743516.304814</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>176304388.023208</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>210086691.619224</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>245040419.455523</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>262771945.533674</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>4006.91868168782</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>4004.99506312087</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>3903.83173844522</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>3908.82817648178</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>4037.81467775039</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>4184.60832992483</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>3565.6354351823</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>4126.78594789647</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>3959.56136048995</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>4489.80646025324</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>4415.41673711427</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>4365.01631317663</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>4195.77770382659</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>4134.84712386417</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>4216.30164715861</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4720.40019766895</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4687.21664279266</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4533.15541062421</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4532.81150732723</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4678.95390529547</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4858.57027255984</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4118.70925179988</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4739.0440984298</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4543.8356107755</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5186.33918694565</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5082.34881105133</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5032.69545196927</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>4807.31937117824</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>4719.19203305578</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>5002.16286604002</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>64.05</t>
+          <t>2183.75432366237</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>53.36</t>
+          <t>2112.65111979316</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>53.63</t>
+          <t>2044.26726001742</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>47.79</t>
+          <t>2297.17374123947</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>2486.67624060495</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>58.68</t>
+          <t>2847.25664877912</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>2432.65066122194</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>37.46</t>
+          <t>2722.81729745513</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>3059.03083731146</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>3345.33148452363</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>3577.48983631473</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>4339.13982305009</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>5320.73796135974</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>5961.29617365826</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>4978.86495064032</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>223308549.177925</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>224223829.018145</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18.37</t>
+          <t>194606590.064639</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>235713144.618625</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>297858904.898829</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>400825107.591998</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>315259530.883817</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>319652529.238009</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19.19</t>
+          <t>303569846.179123</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-11.36</t>
+          <t>302335595.741737</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>284259649.213813</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-6.91</t>
+          <t>353617519.48205</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>348679971.893712</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>339772969.68389</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-12.7</t>
+          <t>260915307.862168</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-48.87</t>
+          <t>3077.55815565765</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-49.75</t>
+          <t>2989.78848671855</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-49.89</t>
+          <t>2760.72266341456</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-55.14</t>
+          <t>2924.43956971278</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-54.3</t>
+          <t>3136.08578646415</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-53.47</t>
+          <t>3538.13613509204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-62.52</t>
+          <t>2954.38987457375</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-58.32</t>
+          <t>3079.71544903443</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-66.58</t>
+          <t>3638.92937598667</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-62.69</t>
+          <t>4078.39464551972</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-59.79</t>
+          <t>4367.58618560208</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-59.05</t>
+          <t>5158.88821386639</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-55.4</t>
+          <t>6223.19467713802</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-60.88</t>
+          <t>6853.35799509956</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-60.45</t>
+          <t>5595.79028406079</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>655.543</t>
+          <t>621641477.107514</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>653.812</t>
+          <t>638956399.770773</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>634.842</t>
+          <t>502229780.789643</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>643.603</t>
+          <t>594896737.830089</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>673.34</t>
+          <t>760271245.666278</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>707.08</t>
+          <t>951363911.993909</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>611.705</t>
+          <t>846510797.955028</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>717.138</t>
+          <t>835407809.763408</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>684.216</t>
+          <t>863116756.267458</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>771.824</t>
+          <t>752851917.542665</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>767.026</t>
+          <t>780697944.271265</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>775.998</t>
+          <t>877183990.326679</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>764.902</t>
+          <t>885847514.312581</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>773.192</t>
+          <t>891561272.77481</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>812.683</t>
+          <t>713548591.845243</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>490.702</t>
+          <t>-893.803831995282</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>492.634</t>
+          <t>-877.137366925392</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>482.105</t>
+          <t>-716.455403397146</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>489.421</t>
+          <t>-627.265828473319</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>512.41</t>
+          <t>-649.409545859193</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>537.032</t>
+          <t>-690.879486312916</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>469.854</t>
+          <t>-521.739213351805</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>554.452</t>
+          <t>-356.898151579299</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>527.666</t>
+          <t>-579.898538675215</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>589.533</t>
+          <t>-733.063160996098</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>587.771</t>
+          <t>-790.096349287349</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>593.379</t>
+          <t>-819.748390816298</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>588.491</t>
+          <t>-902.456715778277</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>593.366</t>
+          <t>-892.061821441303</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>609.224</t>
+          <t>-616.925333420476</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>787.624</t>
+          <t>-398332927.929589</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>775.415</t>
+          <t>-414732570.752627</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>657.844</t>
+          <t>-307623190.725005</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>735.589</t>
+          <t>-359183593.211464</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>868.891</t>
+          <t>-462412340.767449</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1044.004</t>
+          <t>-550538804.401911</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>847.892</t>
+          <t>-531251267.071211</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>864.158</t>
+          <t>-515755280.525398</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>847.471</t>
+          <t>-559546910.088335</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>864.545</t>
+          <t>-450516321.800928</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>808.226</t>
+          <t>-496438295.057453</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>887.051</t>
+          <t>-523566470.844629</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>836.182</t>
+          <t>-537167542.418869</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>840.103</t>
+          <t>-551788303.090919</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>752.718</t>
+          <t>-452633283.983076</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1385.82335</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1423.35312</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1377.26698</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1476.38768</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1473.61581</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1515.93832</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1418.21509</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1626.93416</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1868.283</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1984.44397</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2041.98878</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2193.14696</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2538.99753</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2825.1127</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2576.19549</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>327.788</t>
+          <t>0.0408082018147764</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>322.392</t>
+          <t>0.0376896455875792</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>312.542</t>
+          <t>0.0495962516759357</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>316.741</t>
+          <t>0.0447526145337143</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>328.28</t>
+          <t>0.0405197614288493</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>344.337</t>
+          <t>0.0421049528694169</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>300.668</t>
+          <t>0.0469073191731178</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>347.635</t>
+          <t>0.0580598351060868</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>320.035</t>
+          <t>0.0485127775549195</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>362.139</t>
+          <t>0.0429817634714068</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>346.55</t>
+          <t>0.0518902133423115</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>342.769</t>
+          <t>0.0427299673264274</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>321.707</t>
+          <t>0.051520688176504</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>308.102</t>
+          <t>0.0377331288637923</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>318.482</t>
+          <t>0.0303310725219007</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1616.02247943738</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1715.50960720146</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1667.34448396809</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1754.22786698853</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1785.88735535493</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1708.42222994882</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1795.89572328168</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1963.83622744647</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2341.0084328578</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2657.18545419359</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2726.00838892361</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2910.50556607688</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3330.69237946551</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4211.27127438239</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3969.63156938789</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>556.1</t>
+          <t>1838.78028224347</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>576.15</t>
+          <t>1951.70874750034</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>575.748</t>
+          <t>1896.64032042978</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>642.973</t>
+          <t>1995.10864087904</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>648.345</t>
+          <t>2031.06693944933</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>648.997</t>
+          <t>1942.8079854763</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>702.041</t>
+          <t>2027.75751254768</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>748.019</t>
+          <t>2217.01603428793</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>773.818</t>
+          <t>2649.87773934298</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>847.807</t>
+          <t>3024.69870145227</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>808.549</t>
+          <t>3105.22631611993</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>801.214</t>
+          <t>3318.28575340782</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>771.759</t>
+          <t>3798.83718075924</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>865.292</t>
+          <t>4801.04665285912</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>862.057</t>
+          <t>4526.25911690874</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-11.76</t>
+          <t>10387.5856369219</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-14.5</t>
+          <t>10472.6167481845</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-16.26</t>
+          <t>9483.38162869941</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>10201.0690177384</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>10220.2398503971</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-17.25</t>
+          <t>10254.1775437209</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-33.07</t>
+          <t>10625.9934267763</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-25.88</t>
+          <t>11585.0704704321</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-31.81</t>
+          <t>13726.6270515646</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-30.46</t>
+          <t>15507.6288577581</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-27.31</t>
+          <t>15925.640501504</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-25.94</t>
+          <t>17769.8778930057</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>21012.7662506392</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-31.43</t>
+          <t>24984.4029645788</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-29.33</t>
+          <t>24997.3651176415</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>4.533</t>
+          <t>1838.78028224347</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4.379</t>
+          <t>1971.81963499446</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.901</t>
+          <t>2014.16080919266</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4.012</t>
+          <t>2105.0491934226</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.539</t>
+          <t>2187.32487864978</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5.034</t>
+          <t>2220.06132249716</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4.478</t>
+          <t>2341.96233993632</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4.286</t>
+          <t>2416.85037926708</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.546</t>
+          <t>2406.06824787509</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.335</t>
+          <t>2461.64909418327</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.889</t>
+          <t>2512.31847011829</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>3.163</t>
+          <t>2574.27894368699</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.504</t>
+          <t>2626.41985086363</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3048.45170473549</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.364</t>
+          <t>2961.89450481308</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1616.02247943738</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1733.12184215755</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1770.48890676647</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1850.65172602171</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1922.98613329567</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1951.74472640863</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2073.73783740309</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2140.18170002683</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2124.94077630928</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2160.56270123431</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2203.17336956751</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2255.01404420631</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2299.23424464493</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2670.20692419726</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2593.97155767355</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1358.93245775653</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1357.14530249966</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1348.45227957022</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1444.88629912096</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1442.58140055067</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1511.2096245237</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1361.36418745232</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1530.27083571207</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1758.04608065702</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1859.37692854773</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2062.21746388007</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2187.51092659218</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2732.02415924076</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2811.66718714088</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2575.92271309126</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>490702234.807561</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>492634489.533981</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>482104880.744501</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>489420705.578407</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>512409541.847644</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>537032008.572635</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>469854361.45134</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>554451718.609528</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>527666227.816671</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>589532847.680305</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>587770846.955639</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>593379359.17894</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>588490775.999053</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>593366116.942693</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>609224101.700199</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>655542965.593269</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>653811703.128332</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>634842335.028257</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>643603285.946705</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>673340019.452608</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>707080205.418008</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>611705343.173336</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>717137963.024403</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>684215933.19612</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>771823890.570913</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>767026350.330811</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>775998440.007873</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>764901532.71713</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>773191519.531981</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>812683202.679585</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>327788296.770841</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>322392117.655215</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>312541635.526216</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>316740582.810686</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>328280124.889305</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>344337058.000144</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>300667634.55923</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>347634791.372373</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>320035309.27817</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>362139087.215833</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>346549920.00284</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>342769340.774915</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>321707070.91782</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>308102378.358443</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>318482155.64948</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>138874.446687167</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>139488.262001645</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>140044.246782362</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>141987.657087953</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>143908.239551269</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>145532.567350409</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>148518.699858705</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>151325.446256559</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>150581.137128626</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>148818.629624851</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>150919.65916683</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>154191.416391832</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>159111.861238722</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>163839.80861896</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>162466.36194054</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>122463.736798588</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>123005.017926314</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>123495.302319692</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>125209.060997641</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>126902.689385716</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>128335.071345203</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>131772.967257186</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>134354.368171712</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>133263.808734455</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>131304.73504799</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>133117.864507571</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>135939.780428245</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>140257.853856829</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>143503.761848436</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>144492.532243455</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>272137948.345955</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>273340778.991406</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>274430285.096707</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>278238586.090692</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>282002153.713565</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>285185181.586899</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>244531553.853267</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>288899268.348295</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>277160855.202434</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>284000169.133413</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>286041214.56216</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>287986878.933645</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>300122877.824299</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>306882575.853023</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>307779660.295915</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>239979570.570101</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>241040263.441192</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>242001023.264924</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>245359299.619592</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>248678128.718725</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>251485020.101561</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>216960210.868469</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>256499350.402692</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>245286440.92271</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>250577276.888324</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>252301097.510267</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>253897875.799843</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>264559728.038222</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>271436883.391728</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>264648734.990132</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153249373821671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.151591592079525</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.141357934736138</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.131085475404161</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.13503866866876</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.137628540907754</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.134641513454121</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.138774875738712</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.123858063604186</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.171829178515103</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.181345393421768</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.184575841473869</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.19112187778463</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207927195251845</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.211989600542139</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.169808085044118</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.176824940679784</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.168692369777653</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.160217209274112</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.174665667557867</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.179910216418803</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.187035676667841</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.18621192661329</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.133184295915879</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.195344038586568</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.197423507628787</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.207830894374601</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.199025936164546</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.197474450575818</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.216775569682832</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.676942541134211</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.671583467240692</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.689949695486209</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.708697315321728</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.690295663773374</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.682461242673443</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.678322809878038</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.675013197647998</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.742957640479934</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.632826782898329</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.621231098949445</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.607593264151529</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.609852186050824</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.594598354172337</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.57123482977503</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.238398181075991</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.238066858392622</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.227747502565765</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.222195166027263</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.227510176938149</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.236635290578604</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.237382087297179</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.245302050306835</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.275482376902733</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.28449733732479</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.295094001750916</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.298329438757012</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.301798731469841</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.316575687650561</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.330108019208722</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.257810155388644</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.262483109911152</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.253153617711366</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.247344634029229</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.269763750117847</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.279114814698076</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.28729365765645</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.282124417776103</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.263264598572064</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.280678248137305</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.277918201322617</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.283936834437297</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.270321088442263</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.262729373640372</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.278962492441108</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.503791663535365</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.499450031696226</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.519098879722869</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.530460199943508</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.502726072944004</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.48424989472332</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.475324255046371</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.472573531917062</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.461253024525203</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.434824414537904</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.426987796926467</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.417733726805691</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.427880180087895</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.420694938709067</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.39092948835017</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>6810.28788</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6759.79225</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>6504.52899</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>7022.21424</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>7201.39947</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>7612.00423</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7085.95531</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>7660.96435</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>9137.04683</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>10679.72391</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>11410.39724</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>12906.4076</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>15298.69514</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>17266.45712</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>16001.56341</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3197.71274</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3308.85405</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3245.0926</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3439.99494</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3473.64834</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>3454.01761</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3389.1217</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>3747.28687</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>4407.92382</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>4884.07563</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>5167.44378</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>5505.79668</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>6530.86134</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>7612.71384</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>7102.18183</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>8540.10449177539</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8906.54079634492</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>9298.47153182451</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>9715.44255502075</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>10129.7218552802</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>10575.0429322389</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10878.9484176219</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>11000.1283463253</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>11266.8232314971</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>11529.1787391199</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>11932.1325426299</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>12320.7451710381</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>12719.6954845692</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>12822.9626287163</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>12793.4869850017</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
